--- a/discord/trader_mir_commons_portfolio_2026-05-25_v2.xlsx
+++ b/discord/trader_mir_commons_portfolio_2026-05-25_v2.xlsx
@@ -474,7 +474,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N15"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -568,7 +568,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -585,13 +585,13 @@
         <v>250</v>
       </c>
       <c r="E2" s="3" t="n">
-        <v>44.75</v>
+        <v>15.44</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>140.83</v>
+        <v>16.03</v>
       </c>
       <c r="G2" s="4" t="n">
-        <v>2.147039106145252</v>
+        <v>0.03821243523316073</v>
       </c>
       <c r="H2" s="3" t="n">
         <v>659.1799999999999</v>
@@ -602,21 +602,21 @@
       <c r="J2" s="5" t="n">
         <v>0.1311629600412635</v>
       </c>
-      <c r="K2" s="4" t="n">
-        <v>2.015876146103988</v>
+      <c r="K2" s="6" t="n">
+        <v>-0.09295052480810273</v>
       </c>
       <c r="L2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -633,13 +633,13 @@
         <v>250</v>
       </c>
       <c r="E3" s="3" t="n">
-        <v>13</v>
+        <v>44.75</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>16.35</v>
+        <v>140.83</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>0.2576923076923078</v>
+        <v>2.147039106145252</v>
       </c>
       <c r="H3" s="3" t="n">
         <v>659.1799999999999</v>
@@ -651,20 +651,20 @@
         <v>0.1311629600412635</v>
       </c>
       <c r="K3" s="4" t="n">
-        <v>0.1265293476510443</v>
+        <v>2.015876146103988</v>
       </c>
       <c r="L3" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M3" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="N3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -674,35 +674,35 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="D4" s="2" t="n">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="E4" s="3" t="n">
-        <v>33.55</v>
+        <v>5.11</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>119.84</v>
-      </c>
-      <c r="G4" s="4" t="n">
-        <v>2.571982116244412</v>
+        <v>4.18</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>-0.1819960861056752</v>
       </c>
       <c r="H4" s="3" t="n">
-        <v>659.1799999999999</v>
+        <v>660.91</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>745.64</v>
       </c>
       <c r="J4" s="5" t="n">
-        <v>0.1311629600412635</v>
-      </c>
-      <c r="K4" s="4" t="n">
-        <v>2.440819156203148</v>
+        <v>0.1282020244813969</v>
+      </c>
+      <c r="K4" s="6" t="n">
+        <v>-0.3101981105870721</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="M4" s="2" t="n">
         <v>2</v>
@@ -712,7 +712,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>INFQ</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -722,35 +722,35 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="D5" s="2" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E5" s="3" t="n">
-        <v>40</v>
+        <v>13</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>56.83</v>
+        <v>16.35</v>
       </c>
       <c r="G5" s="4" t="n">
-        <v>0.42075</v>
+        <v>0.2576923076923078</v>
       </c>
       <c r="H5" s="3" t="n">
-        <v>650.33</v>
+        <v>659.1799999999999</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>745.64</v>
       </c>
       <c r="J5" s="5" t="n">
-        <v>0.1465563636922792</v>
+        <v>0.1311629600412635</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>0.2741936363077208</v>
+        <v>0.1265293476510443</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="M5" s="2" t="n">
         <v>0</v>
@@ -760,7 +760,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>KRKNF</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -770,45 +770,45 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="D6" s="2" t="n">
-        <v>216</v>
+        <v>250</v>
       </c>
       <c r="E6" s="3" t="n">
-        <v>5</v>
+        <v>33.55</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>5.3065</v>
+        <v>119.84</v>
       </c>
       <c r="G6" s="4" t="n">
-        <v>0.06129999999999995</v>
+        <v>2.571982116244412</v>
       </c>
       <c r="H6" s="3" t="n">
-        <v>671.29</v>
+        <v>659.1799999999999</v>
       </c>
       <c r="I6" s="3" t="n">
         <v>745.64</v>
       </c>
       <c r="J6" s="5" t="n">
-        <v>0.1107569008923119</v>
-      </c>
-      <c r="K6" s="6" t="n">
-        <v>-0.0494569008923119</v>
+        <v>0.1311629600412635</v>
+      </c>
+      <c r="K6" s="4" t="n">
+        <v>2.440819156203148</v>
       </c>
       <c r="L6" s="2" t="n">
         <v>1</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -818,45 +818,45 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="D7" s="2" t="n">
-        <v>11</v>
+        <v>258</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>946.9</v>
-      </c>
-      <c r="G7" s="6" t="n">
-        <v>-0.05310000000000002</v>
+        <v>56.83</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>0.42075</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>748.17</v>
+        <v>650.33</v>
       </c>
       <c r="I7" s="3" t="n">
         <v>745.64</v>
       </c>
       <c r="J7" s="5" t="n">
-        <v>-0.00338158439926751</v>
-      </c>
-      <c r="K7" s="6" t="n">
-        <v>-0.04971841560073251</v>
+        <v>0.1465563636922792</v>
+      </c>
+      <c r="K7" s="4" t="n">
+        <v>0.2741936363077208</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>KRKNF</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -866,45 +866,45 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="D8" s="2" t="n">
-        <v>250</v>
+        <v>216</v>
       </c>
       <c r="E8" s="3" t="n">
-        <v>63.41333333333333</v>
+        <v>5</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>64.45999999999999</v>
+        <v>5.3065</v>
       </c>
       <c r="G8" s="4" t="n">
-        <v>0.01650546677880561</v>
+        <v>0.06129999999999995</v>
       </c>
       <c r="H8" s="3" t="n">
-        <v>659.1799999999999</v>
+        <v>671.29</v>
       </c>
       <c r="I8" s="3" t="n">
         <v>745.64</v>
       </c>
       <c r="J8" s="5" t="n">
-        <v>0.1311629600412635</v>
+        <v>0.1107569008923119</v>
       </c>
       <c r="K8" s="6" t="n">
-        <v>-0.1146574932624578</v>
+        <v>-0.0494569008923119</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -914,35 +914,35 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="D9" s="2" t="n">
-        <v>250</v>
+        <v>11</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>7.595000000000001</v>
+        <v>1000</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>5.4</v>
+        <v>946.9</v>
       </c>
       <c r="G9" s="6" t="n">
-        <v>-0.2890059249506254</v>
+        <v>-0.05310000000000002</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>659.1799999999999</v>
+        <v>748.17</v>
       </c>
       <c r="I9" s="3" t="n">
         <v>745.64</v>
       </c>
       <c r="J9" s="5" t="n">
-        <v>0.1311629600412635</v>
+        <v>-0.00338158439926751</v>
       </c>
       <c r="K9" s="6" t="n">
-        <v>-0.4201688849918889</v>
+        <v>-0.04971841560073251</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M9" s="2" t="n">
         <v>1</v>
@@ -952,7 +952,7 @@
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
@@ -969,13 +969,13 @@
         <v>250</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>9.98</v>
+        <v>63.41333333333333</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>29.25</v>
+        <v>64.45999999999999</v>
       </c>
       <c r="G10" s="4" t="n">
-        <v>1.930861723446894</v>
+        <v>0.01650546677880561</v>
       </c>
       <c r="H10" s="3" t="n">
         <v>659.1799999999999</v>
@@ -986,21 +986,21 @@
       <c r="J10" s="5" t="n">
         <v>0.1311629600412635</v>
       </c>
-      <c r="K10" s="4" t="n">
-        <v>1.79969876340563</v>
+      <c r="K10" s="6" t="n">
+        <v>-0.1146574932624578</v>
       </c>
       <c r="L10" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M10" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>2</v>
       </c>
       <c r="N10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1017,13 +1017,13 @@
         <v>250</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>16.75</v>
+        <v>7.595000000000001</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>10.93</v>
+        <v>5.4</v>
       </c>
       <c r="G11" s="6" t="n">
-        <v>-0.3474626865671642</v>
+        <v>-0.2890059249506254</v>
       </c>
       <c r="H11" s="3" t="n">
         <v>659.1799999999999</v>
@@ -1035,20 +1035,20 @@
         <v>0.1311629600412635</v>
       </c>
       <c r="K11" s="6" t="n">
-        <v>-0.4786256466084277</v>
+        <v>-0.4201688849918889</v>
       </c>
       <c r="L11" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M11" s="2" t="n">
         <v>1</v>
-      </c>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="N11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -1065,13 +1065,13 @@
         <v>250</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>50</v>
+        <v>9.98</v>
       </c>
       <c r="F12" s="3" t="n">
-        <v>74.27</v>
+        <v>29.25</v>
       </c>
       <c r="G12" s="4" t="n">
-        <v>0.4853999999999999</v>
+        <v>1.930861723446894</v>
       </c>
       <c r="H12" s="3" t="n">
         <v>659.1799999999999</v>
@@ -1083,20 +1083,20 @@
         <v>0.1311629600412635</v>
       </c>
       <c r="K12" s="4" t="n">
-        <v>0.3542370399587365</v>
+        <v>1.79969876340563</v>
       </c>
       <c r="L12" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" s="2" t="n">
         <v>2</v>
-      </c>
-      <c r="M12" s="2" t="n">
-        <v>0</v>
       </c>
       <c r="N12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -1113,13 +1113,13 @@
         <v>250</v>
       </c>
       <c r="E13" s="3" t="n">
-        <v>667</v>
+        <v>16.75</v>
       </c>
       <c r="F13" s="3" t="n">
-        <v>1478.69</v>
-      </c>
-      <c r="G13" s="4" t="n">
-        <v>1.216926536731634</v>
+        <v>10.93</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.3474626865671642</v>
       </c>
       <c r="H13" s="3" t="n">
         <v>659.1799999999999</v>
@@ -1130,11 +1130,11 @@
       <c r="J13" s="5" t="n">
         <v>0.1311629600412635</v>
       </c>
-      <c r="K13" s="4" t="n">
-        <v>1.085763576690371</v>
+      <c r="K13" s="6" t="n">
+        <v>-0.4786256466084277</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="M13" s="2" t="n">
         <v>0</v>
@@ -1144,7 +1144,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1154,32 +1154,32 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="D14" s="2" t="n">
-        <v>258</v>
+        <v>250</v>
       </c>
       <c r="E14" s="3" t="n">
-        <v>25.9</v>
+        <v>50</v>
       </c>
       <c r="F14" s="3" t="n">
-        <v>15.62</v>
-      </c>
-      <c r="G14" s="6" t="n">
-        <v>-0.396911196911197</v>
+        <v>74.27</v>
+      </c>
+      <c r="G14" s="4" t="n">
+        <v>0.4853999999999999</v>
       </c>
       <c r="H14" s="3" t="n">
-        <v>650.33</v>
+        <v>659.1799999999999</v>
       </c>
       <c r="I14" s="3" t="n">
         <v>745.64</v>
       </c>
       <c r="J14" s="5" t="n">
-        <v>0.1465563636922792</v>
-      </c>
-      <c r="K14" s="6" t="n">
-        <v>-0.5434675606034761</v>
+        <v>0.1311629600412635</v>
+      </c>
+      <c r="K14" s="4" t="n">
+        <v>0.3542370399587365</v>
       </c>
       <c r="L14" s="2" t="n">
         <v>2</v>
@@ -1192,7 +1192,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1209,13 +1209,13 @@
         <v>250</v>
       </c>
       <c r="E15" s="3" t="n">
-        <v>7.4</v>
+        <v>667</v>
       </c>
       <c r="F15" s="3" t="n">
-        <v>8.08</v>
+        <v>1478.69</v>
       </c>
       <c r="G15" s="4" t="n">
-        <v>0.09189189189189186</v>
+        <v>1.216926536731634</v>
       </c>
       <c r="H15" s="3" t="n">
         <v>659.1799999999999</v>
@@ -1226,8 +1226,8 @@
       <c r="J15" s="5" t="n">
         <v>0.1311629600412635</v>
       </c>
-      <c r="K15" s="6" t="n">
-        <v>-0.0392710681493716</v>
+      <c r="K15" s="4" t="n">
+        <v>1.085763576690371</v>
       </c>
       <c r="L15" s="2" t="n">
         <v>2</v>
@@ -1236,6 +1236,102 @@
         <v>0</v>
       </c>
       <c r="N15" s="2" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>SOFI</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-09</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="n">
+        <v>258</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>25.9</v>
+      </c>
+      <c r="F16" s="3" t="n">
+        <v>15.62</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.396911196911197</v>
+      </c>
+      <c r="H16" s="3" t="n">
+        <v>650.33</v>
+      </c>
+      <c r="I16" s="3" t="n">
+        <v>745.64</v>
+      </c>
+      <c r="J16" s="5" t="n">
+        <v>0.1465563636922792</v>
+      </c>
+      <c r="K16" s="6" t="n">
+        <v>-0.5434675606034761</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="2" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="n">
+        <v>250</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="F17" s="3" t="n">
+        <v>8.08</v>
+      </c>
+      <c r="G17" s="4" t="n">
+        <v>0.09189189189189186</v>
+      </c>
+      <c r="H17" s="3" t="n">
+        <v>659.1799999999999</v>
+      </c>
+      <c r="I17" s="3" t="n">
+        <v>745.64</v>
+      </c>
+      <c r="J17" s="5" t="n">
+        <v>0.1311629600412635</v>
+      </c>
+      <c r="K17" s="6" t="n">
+        <v>-0.0392710681493716</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1248,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N85"/>
+  <dimension ref="A1:N83"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1349,7 +1445,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -1364,44 +1460,44 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>246</v>
+        <v>138</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>12.03333333333333</v>
+        <v>6</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>15.11</v>
-      </c>
-      <c r="H4" s="4" t="n">
-        <v>0.2556786703601108</v>
+        <v>4.18</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.3033333333333334</v>
       </c>
       <c r="I4" s="3" t="n">
         <v>659.1799999999999</v>
       </c>
       <c r="J4" s="3" t="n">
-        <v>742.72</v>
+        <v>695.41</v>
       </c>
       <c r="K4" s="5" t="n">
-        <v>0.1267332139931431</v>
-      </c>
-      <c r="L4" s="4" t="n">
-        <v>0.1289454563669676</v>
+        <v>0.05496222579568558</v>
+      </c>
+      <c r="L4" s="6" t="n">
+        <v>-0.3582955591290189</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
@@ -1416,44 +1512,44 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>138</v>
+        <v>0</v>
       </c>
       <c r="F5" s="3" t="n">
-        <v>6</v>
+        <v>19</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>4.18</v>
-      </c>
-      <c r="H5" s="6" t="n">
-        <v>-0.3033333333333334</v>
+        <v>43.33333333333334</v>
+      </c>
+      <c r="H5" s="4" t="n">
+        <v>1.280701754385965</v>
       </c>
       <c r="I5" s="3" t="n">
         <v>659.1799999999999</v>
       </c>
       <c r="J5" s="3" t="n">
-        <v>695.41</v>
+        <v>659.1799999999999</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0.05496222579568558</v>
-      </c>
-      <c r="L5" s="6" t="n">
-        <v>-0.3582955591290189</v>
+        <v>0</v>
+      </c>
+      <c r="L5" s="4" t="n">
+        <v>1.280701754385965</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
@@ -1463,7 +1559,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-08-06</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
@@ -1472,40 +1568,40 @@
         </is>
       </c>
       <c r="E6" s="2" t="n">
-        <v>0</v>
+        <v>42</v>
       </c>
       <c r="F6" s="3" t="n">
-        <v>19</v>
+        <v>43</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>43.33333333333334</v>
+        <v>83</v>
       </c>
       <c r="H6" s="4" t="n">
-        <v>1.280701754385965</v>
+        <v>0.9302325581395349</v>
       </c>
       <c r="I6" s="3" t="n">
-        <v>659.1799999999999</v>
+        <v>632.78</v>
       </c>
       <c r="J6" s="3" t="n">
         <v>659.1799999999999</v>
       </c>
       <c r="K6" s="5" t="n">
-        <v>0</v>
+        <v>0.04172066120926701</v>
       </c>
       <c r="L6" s="4" t="n">
-        <v>1.280701754385965</v>
+        <v>0.8885118969302678</v>
       </c>
       <c r="M6" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N6" s="2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1515,7 +1611,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1524,28 +1620,28 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>42</v>
+        <v>8</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>43</v>
+        <v>3.22</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>83</v>
-      </c>
-      <c r="H7" s="4" t="n">
-        <v>0.9302325581395349</v>
+        <v>2.3</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.2857142857142858</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>632.78</v>
+        <v>650.33</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>659.1799999999999</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.04172066120926701</v>
-      </c>
-      <c r="L7" s="4" t="n">
-        <v>0.8885118969302678</v>
+        <v>0.01360847569695372</v>
+      </c>
+      <c r="L7" s="6" t="n">
+        <v>-0.2993227614112395</v>
       </c>
       <c r="M7" s="2" t="n">
         <v>2</v>
@@ -1557,7 +1653,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>RZLV</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1567,7 +1663,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1576,40 +1672,40 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>3.22</v>
+        <v>7.12</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>2.3</v>
+        <v>5.36</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.2857142857142858</v>
+        <v>-0.247191011235955</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>650.33</v>
+        <v>659.1799999999999</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>659.1799999999999</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0.01360847569695372</v>
+        <v>0</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-0.2993227614112395</v>
+        <v>-0.247191011235955</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1617,199 +1713,145 @@
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-15</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F9" s="3" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="G9" s="3" t="n">
-        <v>4.035</v>
-      </c>
-      <c r="H9" s="6" t="n">
-        <v>-0.2103718199608611</v>
-      </c>
-      <c r="I9" s="3" t="n">
-        <v>660.91</v>
-      </c>
-      <c r="J9" s="3" t="n">
-        <v>659.1799999999999</v>
-      </c>
-      <c r="K9" s="5" t="n">
-        <v>-0.00261760300192162</v>
-      </c>
-      <c r="L9" s="6" t="n">
-        <v>-0.2077542169589395</v>
-      </c>
+      <c r="C9" s="2" t="n"/>
+      <c r="D9" s="2" t="n"/>
+      <c r="E9" s="2" t="n"/>
+      <c r="F9" s="3" t="n"/>
+      <c r="G9" s="3" t="n"/>
+      <c r="H9" s="5" t="n"/>
+      <c r="I9" s="3" t="n"/>
+      <c r="J9" s="3" t="n"/>
+      <c r="K9" s="5" t="n"/>
+      <c r="L9" s="5" t="n"/>
       <c r="M9" s="2" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>RZLV</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>2025-09-17</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="3" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="G10" s="3" t="n">
-        <v>5.36</v>
-      </c>
-      <c r="H10" s="6" t="n">
-        <v>-0.247191011235955</v>
-      </c>
-      <c r="I10" s="3" t="n">
-        <v>659.1799999999999</v>
-      </c>
-      <c r="J10" s="3" t="n">
-        <v>659.1799999999999</v>
-      </c>
-      <c r="K10" s="5" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="6" t="n">
-        <v>-0.247191011235955</v>
-      </c>
-      <c r="M10" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="N10" s="2" t="n">
-        <v>1</v>
-      </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>SATS</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n"/>
-      <c r="D11" s="2" t="n"/>
-      <c r="E11" s="2" t="n"/>
-      <c r="F11" s="3" t="n"/>
-      <c r="G11" s="3" t="n"/>
-      <c r="H11" s="5" t="n"/>
-      <c r="I11" s="3" t="n"/>
-      <c r="J11" s="3" t="n"/>
-      <c r="K11" s="5" t="n"/>
-      <c r="L11" s="5" t="n"/>
-      <c r="M11" s="2" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="2" t="n">
-        <v>0</v>
+      <c r="A11" s="7" t="inlineStr">
+        <is>
+          <t>RAW EVENT LOG (chronological)</t>
+        </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="7" t="inlineStr">
-        <is>
-          <t>RAW EVENT LOG (chronological)</t>
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="B13" s="1" t="inlineStr">
+        <is>
+          <t>Ticker</t>
+        </is>
+      </c>
+      <c r="C13" s="1" t="inlineStr">
+        <is>
+          <t>Action</t>
+        </is>
+      </c>
+      <c r="D13" s="1" t="inlineStr">
+        <is>
+          <t>Price</t>
+        </is>
+      </c>
+      <c r="E13" s="1" t="inlineStr">
+        <is>
+          <t>Tag</t>
+        </is>
+      </c>
+      <c r="F13" s="1" t="inlineStr">
+        <is>
+          <t>Source Snippet</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>2025-01-02</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>RGTI</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D14" s="8" t="n"/>
+      <c r="E14" s="8" t="inlineStr"/>
+      <c r="F14" s="8" t="inlineStr">
+        <is>
+          <t>I'm starting a side @account challenge that's compromised only of $RGTI $IONQ</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="1" t="inlineStr">
-        <is>
-          <t>Date</t>
-        </is>
-      </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>Ticker</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>Price</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>Tag</t>
-        </is>
-      </c>
-      <c r="F15" s="1" t="inlineStr">
-        <is>
-          <t>Source Snippet</t>
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>2025-08-06</t>
+        </is>
+      </c>
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>INOD</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>43</v>
+      </c>
+      <c r="E15" s="8" t="inlineStr"/>
+      <c r="F15" s="8" t="inlineStr">
+        <is>
+          <t>$INOD commons added to long term portfolio at 43 cost basis</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>2025-01-02</t>
+          <t>2025-08-28</t>
         </is>
       </c>
       <c r="B16" s="8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="C16" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D16" s="8" t="n"/>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D16" s="9" t="n"/>
       <c r="E16" s="8" t="inlineStr"/>
       <c r="F16" s="8" t="inlineStr">
         <is>
-          <t>I'm starting a side @account challenge that's compromised only of $RGTI $IONQ</t>
+          <t>$SATS to be added to buy and hold account for larger portfolio growth.</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2025-08-06</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
@@ -1818,36 +1860,38 @@
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>43</v>
+        <v>25.9</v>
       </c>
       <c r="E17" s="8" t="inlineStr"/>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>$INOD commons added to long term portfolio at 43 cost basis</t>
+          <t>Adding $SOFI to our commons here at 25.90 before I forget again.</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2025-08-28</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>SATS</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D18" s="9" t="n"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>30</v>
+      </c>
       <c r="E18" s="8" t="inlineStr"/>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>$SATS to be added to buy and hold account for larger portfolio growth.</t>
+          <t>$IREN at 30 as well</t>
         </is>
       </c>
     </row>
@@ -1859,59 +1903,59 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>25.9</v>
+        <v>3.22</v>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>Adding $SOFI to our commons here at 25.90 before I forget again.</t>
+          <t>$LDI commons at 3.22</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>30</v>
+        <v>5.11</v>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>$IREN at 30 as well</t>
+          <t>Adding $BBAI commons at $5.11,</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>RZLV</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1920,38 +1964,42 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>3.22</v>
+        <v>7.12</v>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>$LDI commons at 3.22</t>
+          <t>$RZLV @ $7.12</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="C22" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D22" s="9" t="n">
-        <v>5.11</v>
-      </c>
-      <c r="E22" s="8" t="inlineStr"/>
+        <v>19</v>
+      </c>
+      <c r="E22" s="8" t="inlineStr">
+        <is>
+          <t>RECAP</t>
+        </is>
+      </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>Adding $BBAI commons at $5.11,</t>
+          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
         </is>
       </c>
     </row>
@@ -1963,21 +2011,25 @@
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>RZLV</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>7.12</v>
-      </c>
-      <c r="E23" s="8" t="inlineStr"/>
+        <v>40</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr">
+        <is>
+          <t>RECAP</t>
+        </is>
+      </c>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>$RZLV @ $7.12</t>
+          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
         </is>
       </c>
     </row>
@@ -1994,11 +2046,11 @@
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>19</v>
+        <v>45</v>
       </c>
       <c r="E24" s="8" t="inlineStr">
         <is>
@@ -2019,16 +2071,16 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
@@ -2037,7 +2089,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
+          <t>$INOD - 43  (100% gain achieved) (remaining half of position closed at 83)</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2101,7 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
@@ -2058,7 +2110,7 @@
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>45</v>
+        <v>83</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
@@ -2067,7 +2119,7 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
+          <t>$INOD - 43  (100% gain achieved) (remaining half of position closed at 83)</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2131,7 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
@@ -2088,7 +2140,7 @@
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>43</v>
+        <v>25.9</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
@@ -2097,7 +2149,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>$INOD - 43  (100% gain achieved) (remaining half of position closed at 83)</t>
+          <t>$SOFI - 25.90</t>
         </is>
       </c>
     </row>
@@ -2109,16 +2161,16 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>83</v>
+        <v>30</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -2127,7 +2179,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>$INOD - 43  (100% gain achieved) (remaining half of position closed at 83)</t>
+          <t>$IREN - 30 (100% gain achieved)</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2191,7 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
@@ -2148,7 +2200,7 @@
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>25.9</v>
+        <v>3.22</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -2157,7 +2209,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>$SOFI - 25.90</t>
+          <t>$LDI - 3.22 ( closing @ 2.3 )</t>
         </is>
       </c>
     </row>
@@ -2169,16 +2221,16 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>30</v>
+        <v>2.3</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
@@ -2187,7 +2239,7 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>$IREN - 30 (100% gain achieved)</t>
+          <t>$LDI - 3.22 ( closing @ 2.3 )</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2251,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -2208,7 +2260,7 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>3.22</v>
+        <v>5.11</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
@@ -2217,7 +2269,7 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>$LDI - 3.22 ( closing @ 2.3 )</t>
+          <t>$BBAI - 5.11 (2x weighting) (1/2 position closed @ 4.07, back to equal weight)</t>
         </is>
       </c>
     </row>
@@ -2229,25 +2281,25 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>2.3</v>
+        <v>4.07</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>RECAP OVERRIDDEN</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>$LDI - 3.22 ( closing @ 2.3 )</t>
+          <t>$BBAI - 5.11 (2x weighting) (1/2 position closed @ 4.07, back to equal weight)</t>
         </is>
       </c>
     </row>
@@ -2259,7 +2311,7 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>RZLV</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
@@ -2268,7 +2320,7 @@
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>5.11</v>
+        <v>7.12</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -2277,7 +2329,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>$BBAI - 5.11 (2x weighting) (1/2 position closed @ 4.07, back to equal weight)</t>
+          <t>$RZLV - $7.12 ( closing position @ $5.36 )</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2341,7 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>RZLV</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
@@ -2298,7 +2350,7 @@
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>4.07</v>
+        <v>5.36</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -2307,7 +2359,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>$BBAI - 5.11 (2x weighting) (1/2 position closed @ 4.07, back to equal weight)</t>
+          <t>$RZLV - $7.12 ( closing position @ $5.36 )</t>
         </is>
       </c>
     </row>
@@ -2319,7 +2371,7 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>RZLV</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
@@ -2328,7 +2380,7 @@
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>7.12</v>
+        <v>8.83</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
@@ -2337,7 +2389,7 @@
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>$RZLV - $7.12 ( closing position @ $5.36 )</t>
+          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
         </is>
       </c>
     </row>
@@ -2349,7 +2401,7 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>RZLV</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
@@ -2358,7 +2410,7 @@
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>5.36</v>
+        <v>6.36</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
@@ -2367,7 +2419,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>$RZLV - $7.12 ( closing position @ $5.36 )</t>
+          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
         </is>
       </c>
     </row>
@@ -2379,16 +2431,16 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>8.83</v>
+        <v>6.36</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
@@ -2409,16 +2461,16 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>6.36</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
@@ -2427,7 +2479,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
+          <t>$MP - 64.76 (half sized- will add other half if 65 is held or on a pullback to 57) (position now full sized)</t>
         </is>
       </c>
     </row>
@@ -2439,16 +2491,16 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>6.36</v>
+        <v>10.33</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
@@ -2457,7 +2509,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
+          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
         </is>
       </c>
     </row>
@@ -2469,16 +2521,16 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>64.76000000000001</v>
+        <v>15</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -2487,7 +2539,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>$MP - 64.76 (half sized- will add other half if 65 is held or on a pullback to 57) (position now full sized)</t>
+          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
         </is>
       </c>
     </row>
@@ -2504,15 +2556,15 @@
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>10.33</v>
+        <v>15</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>RECAP OVERRIDDEN</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
@@ -2529,16 +2581,16 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>15</v>
+        <v>33.55</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -2547,7 +2599,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
+          <t>$INTC - $33.55 (closing 1/2 @ $82.55 +150%)</t>
         </is>
       </c>
     </row>
@@ -2559,25 +2611,25 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>15.44</v>
+        <v>82.55</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>RECAP OVERRIDDEN</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
+          <t>$INTC - $33.55 (closing 1/2 @ $82.55 +150%)</t>
         </is>
       </c>
     </row>
@@ -2589,7 +2641,7 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
@@ -2598,7 +2650,7 @@
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>33.55</v>
+        <v>6</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
@@ -2607,7 +2659,7 @@
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>$INTC - $33.55 (closing 1/2 @ $82.55 +150%)</t>
+          <t>$RXRX - $6 ( closing @ $4.18 )</t>
         </is>
       </c>
     </row>
@@ -2619,25 +2671,25 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>82.55</v>
+        <v>4.18</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>RECAP OVERRIDDEN</t>
+          <t>RECAP</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>$INTC - $33.55 (closing 1/2 @ $82.55 +150%)</t>
+          <t>$RXRX - $6 ( closing @ $4.18 )</t>
         </is>
       </c>
     </row>
@@ -2649,7 +2701,7 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
@@ -2658,7 +2710,7 @@
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>6</v>
+        <v>9.98</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
@@ -2667,7 +2719,7 @@
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>$RXRX - $6 ( closing @ $4.18 )</t>
+          <t>$NVTS - $9.98 ( closing 1/2 $NVTS @ 20.87 for just over 100% )</t>
         </is>
       </c>
     </row>
@@ -2679,25 +2731,25 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>4.18</v>
+        <v>20.87</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>RECAP OVERRIDDEN</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>$RXRX - $6 ( closing @ $4.18 )</t>
+          <t>$NVTS - $9.98 ( closing 1/2 $NVTS @ 20.87 for just over 100% )</t>
         </is>
       </c>
     </row>
@@ -2709,7 +2761,7 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
@@ -2718,7 +2770,7 @@
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>9.98</v>
+        <v>16.75</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -2727,7 +2779,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>$NVTS - $9.98 ( closing 1/2 $NVTS @ 20.87 for just over 100% )</t>
+          <t>$PATH - $16.75</t>
         </is>
       </c>
     </row>
@@ -2739,25 +2791,25 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>20.87</v>
+        <v>50</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>RECAP OVERRIDDEN</t>
+          <t>RECAP</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>$NVTS - $9.98 ( closing 1/2 $NVTS @ 20.87 for just over 100% )</t>
+          <t>$SEI - 50</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2821,7 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
@@ -2778,7 +2830,7 @@
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>16.75</v>
+        <v>667</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
@@ -2787,7 +2839,7 @@
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>$PATH - $16.75</t>
+          <t>$SNDK - $667</t>
         </is>
       </c>
     </row>
@@ -2799,7 +2851,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -2808,7 +2860,7 @@
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>50</v>
+        <v>44.75</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
@@ -2817,7 +2869,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>$SEI - 50</t>
+          <t>$AXTI - $44.75 (1/2 out @ 98.60 for 120%)</t>
         </is>
       </c>
     </row>
@@ -2829,16 +2881,16 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>667</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
@@ -2847,7 +2899,7 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>$SNDK - $667</t>
+          <t>$AXTI - $44.75 (1/2 out @ 98.60 for 120%)</t>
         </is>
       </c>
     </row>
@@ -2859,7 +2911,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>INFQ</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2868,7 +2920,7 @@
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>44.75</v>
+        <v>13</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
@@ -2877,7 +2929,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>$AXTI - $44.75 (1/2 out @ 98.60 for 120%)</t>
+          <t>$INFQ - $13 (S/L: 12)</t>
         </is>
       </c>
     </row>
@@ -2889,16 +2941,16 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>98.59999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
@@ -2907,7 +2959,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>$AXTI - $44.75 (1/2 out @ 98.60 for 120%)</t>
+          <t>$TE - $7.40</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2971,7 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
@@ -2928,58 +2980,48 @@
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="E55" s="8" t="inlineStr">
-        <is>
-          <t>RECAP</t>
-        </is>
-      </c>
+        <v>10.33</v>
+      </c>
+      <c r="E55" s="8" t="inlineStr"/>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>$INFQ - $13 (S/L: 12)</t>
+          <t>$AMPX @ $10.33</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="n">
-        <v>7.4</v>
-      </c>
-      <c r="E56" s="8" t="inlineStr">
-        <is>
-          <t>RECAP</t>
-        </is>
-      </c>
+          <t>TRIM</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n"/>
+      <c r="E56" s="8" t="inlineStr"/>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>$TE - $7.40</t>
+          <t>$INOD 100% gain achieved, make it free fam</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -2988,48 +3030,50 @@
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>10.33</v>
+        <v>60</v>
       </c>
       <c r="E57" s="8" t="inlineStr"/>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>$AMPX @ $10.33</t>
+          <t>$IREN is just 3 handles shy of a double. Will be official at 60</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
-        </is>
-      </c>
-      <c r="D58" s="9" t="n"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D58" s="9" t="n">
+        <v>8.83</v>
+      </c>
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>$INOD 100% gain achieved, make it free fam</t>
+          <t>$NB @ $8.83</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
@@ -3038,154 +3082,154 @@
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="E59" s="8" t="inlineStr"/>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>$IREN is just 3 handles shy of a double. Will be official at 60</t>
+          <t>Buying $RXRX @ $6</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D60" s="9" t="n">
-        <v>8.83</v>
+        <v>83</v>
       </c>
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>$NB @ $8.83</t>
+          <t>i’m selling the remaining $INOD commons @ 83.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>6</v>
+        <v>45</v>
       </c>
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Buying $RXRX @ $6</t>
+          <t>Closing out the remaining $RGTI position @ 45 to lock in the over 100% gain on commons.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>i’m selling the remaining $INOD commons @ 83.</t>
+          <t>Adding solar name $SEI @ 50 to the commons port</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>KRKNF</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>45</v>
+        <v>5</v>
       </c>
       <c r="E63" s="8" t="inlineStr"/>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>Closing out the remaining $RGTI position @ 45 to lock in the over 100% gain on commons.</t>
+          <t>$KRKNF @ $5</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>50</v>
+        <v>6.36</v>
       </c>
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Adding solar name $SEI @ 50 to the commons port</t>
+          <t>Selling $NB at 6.36 for a loss,</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>KRKNF</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
@@ -3194,64 +3238,68 @@
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>5</v>
+        <v>64.88</v>
       </c>
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>$KRKNF @ $5</t>
+          <t>Replacing it with $MP at 64.88 but half sized.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>6.36</v>
-      </c>
-      <c r="E66" s="8" t="inlineStr"/>
+        <v>60.6</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDDEN</t>
+        </is>
+      </c>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Selling $NB at 6.36 for a loss,</t>
+          <t>Dropping $RXRX from the commons port @ $4.18 and adding the other half of $MP @ 60.60</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>64.88</v>
+        <v>4.18</v>
       </c>
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Replacing it with $MP at 64.88 but half sized.</t>
+          <t>Dropping $RXRX from the commons port @ $4.18 and adding the other half of $MP @ 60.60</t>
         </is>
       </c>
     </row>
@@ -3263,25 +3311,21 @@
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="E68" s="8" t="inlineStr">
-        <is>
-          <t>OVERRIDDEN</t>
-        </is>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Dropping $RXRX from the commons port @ $4.18 and adding the other half of $MP @ 60.60</t>
+          <t>Closing $LDI @ $2.3</t>
         </is>
       </c>
     </row>
@@ -3293,85 +3337,89 @@
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>4.18</v>
+        <v>667</v>
       </c>
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Dropping $RXRX from the commons port @ $4.18 and adding the other half of $MP @ 60.60</t>
+          <t>Adding $SNDK half sized @ 667</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>Closing $LDI @ $2.3</t>
+          <t>$AXTI @ 44.75 to commons port and selling half of the $BBAI @ $4 that was previously 2x weighting.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>667</v>
-      </c>
-      <c r="E71" s="8" t="inlineStr"/>
+        <v>44.75</v>
+      </c>
+      <c r="E71" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDDEN</t>
+        </is>
+      </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>Adding $SNDK half sized @ 667</t>
+          <t>$AXTI @ 44.75 to commons port and selling half of the $BBAI @ $4 that was previously 2x weighting.</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
@@ -3380,80 +3428,84 @@
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>4</v>
+        <v>15</v>
       </c>
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>$AXTI @ 44.75 to commons port and selling half of the $BBAI @ $4 that was previously 2x weighting.</t>
+          <t>$AMPX UP 77%, SELLING HALF HERE WITH STOP AT 15 ON REMAINDER</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>44.75</v>
+        <v>83.88</v>
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>OVERRIDDEN</t>
+          <t>OVERRIDE_INSERT</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>$AXTI @ 44.75 to commons port and selling half of the $BBAI @ $4 that was previously 2x weighting.</t>
+          <t>INTC up 150% — trim half. No price in source; computed $33.55 × 2.5. Position half-open after this.</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>INFQ</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="E74" s="8" t="inlineStr"/>
+        <v>13</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDDEN</t>
+        </is>
+      </c>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>$AMPX UP 77%, SELLING HALF HERE WITH STOP AT 15 ON REMAINDER</t>
+          <t>$INFQ @ $13 to commons port.</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -3462,105 +3514,93 @@
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>83.88</v>
-      </c>
-      <c r="E75" s="8" t="inlineStr">
-        <is>
-          <t>OVERRIDE_INSERT</t>
-        </is>
-      </c>
+        <v>98.59999999999999</v>
+      </c>
+      <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>INTC up 150% — trim half. No price in source; computed $33.55 × 2.5. Position half-open after this.</t>
+          <t>$AXTI selling half of our position @ 98.60 for 120%</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="E76" s="8" t="inlineStr">
-        <is>
-          <t>OVERRIDDEN</t>
-        </is>
-      </c>
+        <v>20.87</v>
+      </c>
+      <c r="E76" s="8" t="inlineStr"/>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>$INFQ @ $13 to commons port.</t>
+          <t>$NVTS 1/2 sold for @ 20.87 to lock in the 100% gain, standard practice.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="n">
-        <v>98.59999999999999</v>
-      </c>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n"/>
       <c r="E77" s="8" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>$AXTI selling half of our position @ 98.60 for 120%</t>
+          <t>adding $LITE if we dip below 1K again, we should see this double again before the year is up</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="n">
-        <v>20.87</v>
-      </c>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n"/>
       <c r="E78" s="8" t="inlineStr"/>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>$NVTS 1/2 sold for @ 20.87 to lock in the 100% gain, standard practice.</t>
+          <t>$LITE added to commons port.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-05-14</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
@@ -3570,51 +3610,53 @@
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D79" s="9" t="n"/>
-      <c r="E79" s="8" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D79" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E79" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDE_INSERT</t>
+        </is>
+      </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>adding $LITE if we dip below 1K again, we should see this double again before the year is up</t>
+          <t>LITE 'added to commons' on 5/14 with no price. Context 'if we dip below 1K' suggests entry ~$1000.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>1000</v>
-      </c>
-      <c r="E80" s="8" t="inlineStr">
-        <is>
-          <t>OVERRIDE_INSERT</t>
-        </is>
-      </c>
+        <v>7.4</v>
+      </c>
+      <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>LITE 'added to commons' on 5/14 with no price. Context 'if we dip below 1K' suggests entry ~$1000.</t>
+          <t>Adding $TE @ 7.40</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-05-18</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
@@ -3624,122 +3666,72 @@
       </c>
       <c r="C81" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D81" s="9" t="n"/>
+          <t>TRIM</t>
+        </is>
+      </c>
+      <c r="D81" s="9" t="n">
+        <v>886</v>
+      </c>
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>$LITE added to commons port.</t>
+          <t>reducing $LITE by 50% @ 886 ( plan to add back if 800 trades)</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="D82" s="9" t="n">
-        <v>7.4</v>
+        <v>15</v>
       </c>
       <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>Adding $TE @ 7.40</t>
+          <t>$AMPX stopped @ $15 on remaining half of the original position from $10.33.</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-21</t>
         </is>
       </c>
       <c r="B83" s="8" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C83" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D83" s="9" t="n">
-        <v>886</v>
-      </c>
-      <c r="E83" s="8" t="inlineStr"/>
+        <v>15.44</v>
+      </c>
+      <c r="E83" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDE_INSERT</t>
+        </is>
+      </c>
       <c r="F83" s="8" t="inlineStr">
         <is>
-          <t>reducing $LITE by 50% @ 886 ( plan to add back if 800 trades)</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B84" s="8" t="inlineStr">
-        <is>
-          <t>AMPX</t>
-        </is>
-      </c>
-      <c r="C84" s="8" t="inlineStr">
-        <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D84" s="9" t="n">
-        <v>15.44</v>
-      </c>
-      <c r="E84" s="8" t="inlineStr">
-        <is>
-          <t>OVERRIDE_INSERT</t>
-        </is>
-      </c>
-      <c r="F84" s="8" t="inlineStr">
-        <is>
           <t>AMPX stopped at $15, then 'Adding back here @ $15.44 (half sized)'. Re-add missed by parser.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" s="8" t="inlineStr">
-        <is>
-          <t>2026-05-21</t>
-        </is>
-      </c>
-      <c r="B85" s="8" t="inlineStr">
-        <is>
-          <t>AMPX</t>
-        </is>
-      </c>
-      <c r="C85" s="8" t="inlineStr">
-        <is>
-          <t>STOP</t>
-        </is>
-      </c>
-      <c r="D85" s="9" t="n">
-        <v>15</v>
-      </c>
-      <c r="E85" s="8" t="inlineStr"/>
-      <c r="F85" s="8" t="inlineStr">
-        <is>
-          <t>$AMPX stopped @ $15 on remaining half of the original position from $10.33.</t>
         </is>
       </c>
     </row>

--- a/discord/trader_mir_commons_portfolio_2026-05-25_v2.xlsx
+++ b/discord/trader_mir_commons_portfolio_2026-05-25_v2.xlsx
@@ -849,7 +849,7 @@
         <v>3</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N7" s="2" t="inlineStr"/>
     </row>
@@ -1344,7 +1344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N83"/>
+  <dimension ref="A1:N88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1507,7 +1507,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
@@ -1516,7 +1516,7 @@
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F5" s="3" t="n">
         <v>19</v>
@@ -1528,19 +1528,19 @@
         <v>1.280701754385965</v>
       </c>
       <c r="I5" s="3" t="n">
-        <v>659.1799999999999</v>
+        <v>657.41</v>
       </c>
       <c r="J5" s="3" t="n">
         <v>659.1799999999999</v>
       </c>
       <c r="K5" s="5" t="n">
-        <v>0</v>
+        <v>0.002692383748345753</v>
       </c>
       <c r="L5" s="4" t="n">
-        <v>1.280701754385965</v>
+        <v>1.278009370637619</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="N5" s="2" t="n">
         <v>3</v>
@@ -1601,7 +1601,7 @@
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -1620,31 +1620,31 @@
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>3.22</v>
+        <v>56</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="H7" s="6" t="n">
-        <v>-0.2857142857142858</v>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="H7" s="4" t="n">
+        <v>0.5999999999999999</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>650.33</v>
+        <v>647.24</v>
       </c>
       <c r="J7" s="3" t="n">
         <v>659.1799999999999</v>
       </c>
       <c r="K7" s="5" t="n">
-        <v>0.01360847569695372</v>
-      </c>
-      <c r="L7" s="6" t="n">
-        <v>-0.2993227614112395</v>
+        <v>0.01844756195537968</v>
+      </c>
+      <c r="L7" s="4" t="n">
+        <v>0.5815524380446202</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="N7" s="2" t="n">
         <v>2</v>
@@ -1653,7 +1653,7 @@
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>RZLV</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
@@ -1663,7 +1663,7 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
@@ -1672,40 +1672,40 @@
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F8" s="3" t="n">
-        <v>7.12</v>
+        <v>3.22</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>5.36</v>
+        <v>2.3</v>
       </c>
       <c r="H8" s="6" t="n">
-        <v>-0.247191011235955</v>
+        <v>-0.2857142857142858</v>
       </c>
       <c r="I8" s="3" t="n">
-        <v>659.1799999999999</v>
+        <v>650.33</v>
       </c>
       <c r="J8" s="3" t="n">
         <v>659.1799999999999</v>
       </c>
       <c r="K8" s="5" t="n">
-        <v>0</v>
+        <v>0.01360847569695372</v>
       </c>
       <c r="L8" s="6" t="n">
-        <v>-0.247191011235955</v>
+        <v>-0.2993227614112395</v>
       </c>
       <c r="M8" s="2" t="n">
         <v>2</v>
       </c>
       <c r="N8" s="2" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>SATS</t>
+          <t>RZLV</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
@@ -1713,21 +1713,45 @@
           <t>CLOSED</t>
         </is>
       </c>
-      <c r="C9" s="2" t="n"/>
-      <c r="D9" s="2" t="n"/>
-      <c r="E9" s="2" t="n"/>
-      <c r="F9" s="3" t="n"/>
-      <c r="G9" s="3" t="n"/>
-      <c r="H9" s="5" t="n"/>
-      <c r="I9" s="3" t="n"/>
-      <c r="J9" s="3" t="n"/>
-      <c r="K9" s="5" t="n"/>
-      <c r="L9" s="5" t="n"/>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>2025-09-17</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="3" t="n">
+        <v>7.12</v>
+      </c>
+      <c r="G9" s="3" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>-0.247191011235955</v>
+      </c>
+      <c r="I9" s="3" t="n">
+        <v>659.1799999999999</v>
+      </c>
+      <c r="J9" s="3" t="n">
+        <v>659.1799999999999</v>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="6" t="n">
+        <v>-0.247191011235955</v>
+      </c>
       <c r="M9" s="2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="11">
@@ -1846,52 +1870,60 @@
     <row r="17">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-05</t>
         </is>
       </c>
       <c r="B17" s="8" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D17" s="9" t="n">
-        <v>25.9</v>
-      </c>
-      <c r="E17" s="8" t="inlineStr"/>
+        <v>56</v>
+      </c>
+      <c r="E17" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDE_INSERT</t>
+        </is>
+      </c>
       <c r="F17" s="8" t="inlineStr">
         <is>
-          <t>Adding $SOFI to our commons here at 25.90 before I forget again.</t>
+          <t>Per 9/8 message 'We were in at 56 just a few days ago' — entry estimated to 9/5 at $56. SATS was the first commons name explicitly tracked in this cha</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="B18" s="8" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="C18" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D18" s="9" t="n">
-        <v>30</v>
-      </c>
-      <c r="E18" s="8" t="inlineStr"/>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="E18" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDE_INSERT</t>
+        </is>
+      </c>
       <c r="F18" s="8" t="inlineStr">
         <is>
-          <t>$IREN at 30 as well</t>
+          <t>9/8 message 'SATS commons were up nearly 60% on starlink acquisition... Let's harvest some gains'. +60% from $56 entry = $89.60. Recap 9/17 says 'sold</t>
         </is>
       </c>
     </row>
@@ -1903,59 +1935,59 @@
       </c>
       <c r="B19" s="8" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="C19" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D19" s="9" t="n">
-        <v>3.22</v>
+        <v>25.9</v>
       </c>
       <c r="E19" s="8" t="inlineStr"/>
       <c r="F19" s="8" t="inlineStr">
         <is>
-          <t>$LDI commons at 3.22</t>
+          <t>Adding $SOFI to our commons here at 25.90 before I forget again.</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>2025-09-15</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B20" s="8" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C20" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D20" s="9" t="n">
-        <v>5.11</v>
+        <v>30</v>
       </c>
       <c r="E20" s="8" t="inlineStr"/>
       <c r="F20" s="8" t="inlineStr">
         <is>
-          <t>Adding $BBAI commons at $5.11,</t>
+          <t>$IREN at 30 as well</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="B21" s="8" t="inlineStr">
         <is>
-          <t>RZLV</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="C21" s="8" t="inlineStr">
@@ -1964,19 +1996,19 @@
         </is>
       </c>
       <c r="D21" s="9" t="n">
-        <v>7.12</v>
+        <v>3.22</v>
       </c>
       <c r="E21" s="8" t="inlineStr"/>
       <c r="F21" s="8" t="inlineStr">
         <is>
-          <t>$RZLV @ $7.12</t>
+          <t>$LDI commons at 3.22</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-12</t>
         </is>
       </c>
       <c r="B22" s="8" t="inlineStr">
@@ -1994,42 +2026,38 @@
       </c>
       <c r="E22" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>OVERRIDE_INSERT</t>
         </is>
       </c>
       <c r="F22" s="8" t="inlineStr">
         <is>
-          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
+          <t>Explicit entry message: 'I'm going to add it here at this 19 level so we can keep track with the other commons'. Shifts first_entry_date from 9/17 rec</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-15</t>
         </is>
       </c>
       <c r="B23" s="8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="C23" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D23" s="9" t="n">
-        <v>40</v>
-      </c>
-      <c r="E23" s="8" t="inlineStr">
-        <is>
-          <t>RECAP</t>
-        </is>
-      </c>
+        <v>5.11</v>
+      </c>
+      <c r="E23" s="8" t="inlineStr"/>
       <c r="F23" s="8" t="inlineStr">
         <is>
-          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
+          <t>Adding $BBAI commons at $5.11,</t>
         </is>
       </c>
     </row>
@@ -2041,25 +2069,21 @@
       </c>
       <c r="B24" s="8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>RZLV</t>
         </is>
       </c>
       <c r="C24" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D24" s="9" t="n">
-        <v>45</v>
-      </c>
-      <c r="E24" s="8" t="inlineStr">
-        <is>
-          <t>RECAP</t>
-        </is>
-      </c>
+        <v>7.12</v>
+      </c>
+      <c r="E24" s="8" t="inlineStr"/>
       <c r="F24" s="8" t="inlineStr">
         <is>
-          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
+          <t>$RZLV @ $7.12</t>
         </is>
       </c>
     </row>
@@ -2071,7 +2095,7 @@
       </c>
       <c r="B25" s="8" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="C25" s="8" t="inlineStr">
@@ -2080,7 +2104,7 @@
         </is>
       </c>
       <c r="D25" s="9" t="n">
-        <v>43</v>
+        <v>19</v>
       </c>
       <c r="E25" s="8" t="inlineStr">
         <is>
@@ -2089,7 +2113,7 @@
       </c>
       <c r="F25" s="8" t="inlineStr">
         <is>
-          <t>$INOD - 43  (100% gain achieved) (remaining half of position closed at 83)</t>
+          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
         </is>
       </c>
     </row>
@@ -2101,16 +2125,16 @@
       </c>
       <c r="B26" s="8" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="C26" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D26" s="9" t="n">
-        <v>83</v>
+        <v>40</v>
       </c>
       <c r="E26" s="8" t="inlineStr">
         <is>
@@ -2119,7 +2143,7 @@
       </c>
       <c r="F26" s="8" t="inlineStr">
         <is>
-          <t>$INOD - 43  (100% gain achieved) (remaining half of position closed at 83)</t>
+          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
         </is>
       </c>
     </row>
@@ -2131,16 +2155,16 @@
       </c>
       <c r="B27" s="8" t="inlineStr">
         <is>
-          <t>SOFI</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="C27" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D27" s="9" t="n">
-        <v>25.9</v>
+        <v>45</v>
       </c>
       <c r="E27" s="8" t="inlineStr">
         <is>
@@ -2149,7 +2173,7 @@
       </c>
       <c r="F27" s="8" t="inlineStr">
         <is>
-          <t>$SOFI - 25.90</t>
+          <t>$RGTI - 19 (100% gain achieved) (full position closed out at 40 and 45)</t>
         </is>
       </c>
     </row>
@@ -2161,7 +2185,7 @@
       </c>
       <c r="B28" s="8" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C28" s="8" t="inlineStr">
@@ -2170,7 +2194,7 @@
         </is>
       </c>
       <c r="D28" s="9" t="n">
-        <v>30</v>
+        <v>43</v>
       </c>
       <c r="E28" s="8" t="inlineStr">
         <is>
@@ -2179,7 +2203,7 @@
       </c>
       <c r="F28" s="8" t="inlineStr">
         <is>
-          <t>$IREN - 30 (100% gain achieved)</t>
+          <t>$INOD - 43  (100% gain achieved) (remaining half of position closed at 83)</t>
         </is>
       </c>
     </row>
@@ -2191,16 +2215,16 @@
       </c>
       <c r="B29" s="8" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C29" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D29" s="9" t="n">
-        <v>3.22</v>
+        <v>83</v>
       </c>
       <c r="E29" s="8" t="inlineStr">
         <is>
@@ -2209,7 +2233,7 @@
       </c>
       <c r="F29" s="8" t="inlineStr">
         <is>
-          <t>$LDI - 3.22 ( closing @ 2.3 )</t>
+          <t>$INOD - 43  (100% gain achieved) (remaining half of position closed at 83)</t>
         </is>
       </c>
     </row>
@@ -2221,16 +2245,16 @@
       </c>
       <c r="B30" s="8" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>SOFI</t>
         </is>
       </c>
       <c r="C30" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D30" s="9" t="n">
-        <v>2.3</v>
+        <v>25.9</v>
       </c>
       <c r="E30" s="8" t="inlineStr">
         <is>
@@ -2239,7 +2263,7 @@
       </c>
       <c r="F30" s="8" t="inlineStr">
         <is>
-          <t>$LDI - 3.22 ( closing @ 2.3 )</t>
+          <t>$SOFI - 25.90</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2275,7 @@
       </c>
       <c r="B31" s="8" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C31" s="8" t="inlineStr">
@@ -2260,7 +2284,7 @@
         </is>
       </c>
       <c r="D31" s="9" t="n">
-        <v>5.11</v>
+        <v>30</v>
       </c>
       <c r="E31" s="8" t="inlineStr">
         <is>
@@ -2269,7 +2293,7 @@
       </c>
       <c r="F31" s="8" t="inlineStr">
         <is>
-          <t>$BBAI - 5.11 (2x weighting) (1/2 position closed @ 4.07, back to equal weight)</t>
+          <t>$IREN - 30 (100% gain achieved)</t>
         </is>
       </c>
     </row>
@@ -2281,25 +2305,25 @@
       </c>
       <c r="B32" s="8" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="C32" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D32" s="9" t="n">
-        <v>4.07</v>
+        <v>3.22</v>
       </c>
       <c r="E32" s="8" t="inlineStr">
         <is>
-          <t>RECAP OVERRIDDEN</t>
+          <t>RECAP</t>
         </is>
       </c>
       <c r="F32" s="8" t="inlineStr">
         <is>
-          <t>$BBAI - 5.11 (2x weighting) (1/2 position closed @ 4.07, back to equal weight)</t>
+          <t>$LDI - 3.22 ( closing @ 2.3 )</t>
         </is>
       </c>
     </row>
@@ -2311,16 +2335,16 @@
       </c>
       <c r="B33" s="8" t="inlineStr">
         <is>
-          <t>RZLV</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="C33" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D33" s="9" t="n">
-        <v>7.12</v>
+        <v>2.3</v>
       </c>
       <c r="E33" s="8" t="inlineStr">
         <is>
@@ -2329,7 +2353,7 @@
       </c>
       <c r="F33" s="8" t="inlineStr">
         <is>
-          <t>$RZLV - $7.12 ( closing position @ $5.36 )</t>
+          <t>$LDI - 3.22 ( closing @ 2.3 )</t>
         </is>
       </c>
     </row>
@@ -2341,16 +2365,16 @@
       </c>
       <c r="B34" s="8" t="inlineStr">
         <is>
-          <t>RZLV</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="C34" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D34" s="9" t="n">
-        <v>5.36</v>
+        <v>5.11</v>
       </c>
       <c r="E34" s="8" t="inlineStr">
         <is>
@@ -2359,7 +2383,7 @@
       </c>
       <c r="F34" s="8" t="inlineStr">
         <is>
-          <t>$RZLV - $7.12 ( closing position @ $5.36 )</t>
+          <t>$BBAI - 5.11 (2x weighting) (1/2 position closed @ 4.07, back to equal weight)</t>
         </is>
       </c>
     </row>
@@ -2371,25 +2395,25 @@
       </c>
       <c r="B35" s="8" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="C35" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D35" s="9" t="n">
-        <v>8.83</v>
+        <v>4.07</v>
       </c>
       <c r="E35" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>RECAP OVERRIDDEN</t>
         </is>
       </c>
       <c r="F35" s="8" t="inlineStr">
         <is>
-          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
+          <t>$BBAI - 5.11 (2x weighting) (1/2 position closed @ 4.07, back to equal weight)</t>
         </is>
       </c>
     </row>
@@ -2401,16 +2425,16 @@
       </c>
       <c r="B36" s="8" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>RZLV</t>
         </is>
       </c>
       <c r="C36" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D36" s="9" t="n">
-        <v>6.36</v>
+        <v>7.12</v>
       </c>
       <c r="E36" s="8" t="inlineStr">
         <is>
@@ -2419,7 +2443,7 @@
       </c>
       <c r="F36" s="8" t="inlineStr">
         <is>
-          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
+          <t>$RZLV - $7.12 ( closing position @ $5.36 )</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2455,7 @@
       </c>
       <c r="B37" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>RZLV</t>
         </is>
       </c>
       <c r="C37" s="8" t="inlineStr">
@@ -2440,7 +2464,7 @@
         </is>
       </c>
       <c r="D37" s="9" t="n">
-        <v>6.36</v>
+        <v>5.36</v>
       </c>
       <c r="E37" s="8" t="inlineStr">
         <is>
@@ -2449,7 +2473,7 @@
       </c>
       <c r="F37" s="8" t="inlineStr">
         <is>
-          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
+          <t>$RZLV - $7.12 ( closing position @ $5.36 )</t>
         </is>
       </c>
     </row>
@@ -2461,7 +2485,7 @@
       </c>
       <c r="B38" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C38" s="8" t="inlineStr">
@@ -2470,7 +2494,7 @@
         </is>
       </c>
       <c r="D38" s="9" t="n">
-        <v>64.76000000000001</v>
+        <v>8.83</v>
       </c>
       <c r="E38" s="8" t="inlineStr">
         <is>
@@ -2479,7 +2503,7 @@
       </c>
       <c r="F38" s="8" t="inlineStr">
         <is>
-          <t>$MP - 64.76 (half sized- will add other half if 65 is held or on a pullback to 57) (position now full sized)</t>
+          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
         </is>
       </c>
     </row>
@@ -2491,16 +2515,16 @@
       </c>
       <c r="B39" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C39" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D39" s="9" t="n">
-        <v>10.33</v>
+        <v>6.36</v>
       </c>
       <c r="E39" s="8" t="inlineStr">
         <is>
@@ -2509,7 +2533,7 @@
       </c>
       <c r="F39" s="8" t="inlineStr">
         <is>
-          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
+          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
         </is>
       </c>
     </row>
@@ -2521,16 +2545,16 @@
       </c>
       <c r="B40" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C40" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D40" s="9" t="n">
-        <v>15</v>
+        <v>6.36</v>
       </c>
       <c r="E40" s="8" t="inlineStr">
         <is>
@@ -2539,7 +2563,7 @@
       </c>
       <c r="F40" s="8" t="inlineStr">
         <is>
-          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
+          <t>$NB - $8.83 ( closing @ $6.36 - replacing with $MP )</t>
         </is>
       </c>
     </row>
@@ -2551,25 +2575,25 @@
       </c>
       <c r="B41" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C41" s="8" t="inlineStr">
         <is>
-          <t>STOP</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D41" s="9" t="n">
-        <v>15</v>
+        <v>64.76000000000001</v>
       </c>
       <c r="E41" s="8" t="inlineStr">
         <is>
-          <t>RECAP OVERRIDDEN</t>
+          <t>RECAP</t>
         </is>
       </c>
       <c r="F41" s="8" t="inlineStr">
         <is>
-          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
+          <t>$MP - 64.76 (half sized- will add other half if 65 is held or on a pullback to 57) (position now full sized)</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2605,7 @@
       </c>
       <c r="B42" s="8" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C42" s="8" t="inlineStr">
@@ -2590,7 +2614,7 @@
         </is>
       </c>
       <c r="D42" s="9" t="n">
-        <v>33.55</v>
+        <v>10.33</v>
       </c>
       <c r="E42" s="8" t="inlineStr">
         <is>
@@ -2599,7 +2623,7 @@
       </c>
       <c r="F42" s="8" t="inlineStr">
         <is>
-          <t>$INTC - $33.55 (closing 1/2 @ $82.55 +150%)</t>
+          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
         </is>
       </c>
     </row>
@@ -2611,7 +2635,7 @@
       </c>
       <c r="B43" s="8" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C43" s="8" t="inlineStr">
@@ -2620,16 +2644,16 @@
         </is>
       </c>
       <c r="D43" s="9" t="n">
-        <v>82.55</v>
+        <v>15</v>
       </c>
       <c r="E43" s="8" t="inlineStr">
         <is>
-          <t>RECAP OVERRIDDEN</t>
+          <t>RECAP</t>
         </is>
       </c>
       <c r="F43" s="8" t="inlineStr">
         <is>
-          <t>$INTC - $33.55 (closing 1/2 @ $82.55 +150%)</t>
+          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
         </is>
       </c>
     </row>
@@ -2641,25 +2665,25 @@
       </c>
       <c r="B44" s="8" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C44" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>STOP</t>
         </is>
       </c>
       <c r="D44" s="9" t="n">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="E44" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>RECAP OVERRIDDEN</t>
         </is>
       </c>
       <c r="F44" s="8" t="inlineStr">
         <is>
-          <t>$RXRX - $6 ( closing @ $4.18 )</t>
+          <t>$AMPX - $10.33 (closing 1/2 @ 10.33 for 77%, stop @ 15 for remaining position) (stop was hit. Adding back @ $15.44)</t>
         </is>
       </c>
     </row>
@@ -2671,16 +2695,16 @@
       </c>
       <c r="B45" s="8" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C45" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D45" s="9" t="n">
-        <v>4.18</v>
+        <v>33.55</v>
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
@@ -2689,7 +2713,7 @@
       </c>
       <c r="F45" s="8" t="inlineStr">
         <is>
-          <t>$RXRX - $6 ( closing @ $4.18 )</t>
+          <t>$INTC - $33.55 (closing 1/2 @ $82.55 +150%)</t>
         </is>
       </c>
     </row>
@@ -2701,25 +2725,25 @@
       </c>
       <c r="B46" s="8" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C46" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D46" s="9" t="n">
-        <v>9.98</v>
+        <v>82.55</v>
       </c>
       <c r="E46" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>RECAP OVERRIDDEN</t>
         </is>
       </c>
       <c r="F46" s="8" t="inlineStr">
         <is>
-          <t>$NVTS - $9.98 ( closing 1/2 $NVTS @ 20.87 for just over 100% )</t>
+          <t>$INTC - $33.55 (closing 1/2 @ $82.55 +150%)</t>
         </is>
       </c>
     </row>
@@ -2731,25 +2755,25 @@
       </c>
       <c r="B47" s="8" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C47" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D47" s="9" t="n">
-        <v>20.87</v>
+        <v>6</v>
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>RECAP OVERRIDDEN</t>
+          <t>RECAP</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
         <is>
-          <t>$NVTS - $9.98 ( closing 1/2 $NVTS @ 20.87 for just over 100% )</t>
+          <t>$RXRX - $6 ( closing @ $4.18 )</t>
         </is>
       </c>
     </row>
@@ -2761,16 +2785,16 @@
       </c>
       <c r="B48" s="8" t="inlineStr">
         <is>
-          <t>PATH</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C48" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D48" s="9" t="n">
-        <v>16.75</v>
+        <v>4.18</v>
       </c>
       <c r="E48" s="8" t="inlineStr">
         <is>
@@ -2779,7 +2803,7 @@
       </c>
       <c r="F48" s="8" t="inlineStr">
         <is>
-          <t>$PATH - $16.75</t>
+          <t>$RXRX - $6 ( closing @ $4.18 )</t>
         </is>
       </c>
     </row>
@@ -2791,7 +2815,7 @@
       </c>
       <c r="B49" s="8" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="C49" s="8" t="inlineStr">
@@ -2800,7 +2824,7 @@
         </is>
       </c>
       <c r="D49" s="9" t="n">
-        <v>50</v>
+        <v>9.98</v>
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
@@ -2809,7 +2833,7 @@
       </c>
       <c r="F49" s="8" t="inlineStr">
         <is>
-          <t>$SEI - 50</t>
+          <t>$NVTS - $9.98 ( closing 1/2 $NVTS @ 20.87 for just over 100% )</t>
         </is>
       </c>
     </row>
@@ -2821,25 +2845,25 @@
       </c>
       <c r="B50" s="8" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="C50" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D50" s="9" t="n">
-        <v>667</v>
+        <v>20.87</v>
       </c>
       <c r="E50" s="8" t="inlineStr">
         <is>
-          <t>RECAP</t>
+          <t>RECAP OVERRIDDEN</t>
         </is>
       </c>
       <c r="F50" s="8" t="inlineStr">
         <is>
-          <t>$SNDK - $667</t>
+          <t>$NVTS - $9.98 ( closing 1/2 $NVTS @ 20.87 for just over 100% )</t>
         </is>
       </c>
     </row>
@@ -2851,7 +2875,7 @@
       </c>
       <c r="B51" s="8" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>PATH</t>
         </is>
       </c>
       <c r="C51" s="8" t="inlineStr">
@@ -2860,7 +2884,7 @@
         </is>
       </c>
       <c r="D51" s="9" t="n">
-        <v>44.75</v>
+        <v>16.75</v>
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
@@ -2869,7 +2893,7 @@
       </c>
       <c r="F51" s="8" t="inlineStr">
         <is>
-          <t>$AXTI - $44.75 (1/2 out @ 98.60 for 120%)</t>
+          <t>$PATH - $16.75</t>
         </is>
       </c>
     </row>
@@ -2881,16 +2905,16 @@
       </c>
       <c r="B52" s="8" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="C52" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D52" s="9" t="n">
-        <v>98.59999999999999</v>
+        <v>50</v>
       </c>
       <c r="E52" s="8" t="inlineStr">
         <is>
@@ -2899,7 +2923,7 @@
       </c>
       <c r="F52" s="8" t="inlineStr">
         <is>
-          <t>$AXTI - $44.75 (1/2 out @ 98.60 for 120%)</t>
+          <t>$SEI - 50</t>
         </is>
       </c>
     </row>
@@ -2911,7 +2935,7 @@
       </c>
       <c r="B53" s="8" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C53" s="8" t="inlineStr">
@@ -2920,7 +2944,7 @@
         </is>
       </c>
       <c r="D53" s="9" t="n">
-        <v>13</v>
+        <v>667</v>
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
@@ -2929,7 +2953,7 @@
       </c>
       <c r="F53" s="8" t="inlineStr">
         <is>
-          <t>$INFQ - $13 (S/L: 12)</t>
+          <t>$SNDK - $667</t>
         </is>
       </c>
     </row>
@@ -2941,7 +2965,7 @@
       </c>
       <c r="B54" s="8" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C54" s="8" t="inlineStr">
@@ -2950,7 +2974,7 @@
         </is>
       </c>
       <c r="D54" s="9" t="n">
-        <v>7.4</v>
+        <v>44.75</v>
       </c>
       <c r="E54" s="8" t="inlineStr">
         <is>
@@ -2959,7 +2983,7 @@
       </c>
       <c r="F54" s="8" t="inlineStr">
         <is>
-          <t>$TE - $7.40</t>
+          <t>$AXTI - $44.75 (1/2 out @ 98.60 for 120%)</t>
         </is>
       </c>
     </row>
@@ -2971,57 +2995,67 @@
       </c>
       <c r="B55" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C55" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D55" s="9" t="n">
-        <v>10.33</v>
-      </c>
-      <c r="E55" s="8" t="inlineStr"/>
+        <v>98.59999999999999</v>
+      </c>
+      <c r="E55" s="8" t="inlineStr">
+        <is>
+          <t>RECAP</t>
+        </is>
+      </c>
       <c r="F55" s="8" t="inlineStr">
         <is>
-          <t>$AMPX @ $10.33</t>
+          <t>$AXTI - $44.75 (1/2 out @ 98.60 for 120%)</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="8" t="inlineStr">
         <is>
-          <t>2025-10-02</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B56" s="8" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>INFQ</t>
         </is>
       </c>
       <c r="C56" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
-        </is>
-      </c>
-      <c r="D56" s="9" t="n"/>
-      <c r="E56" s="8" t="inlineStr"/>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D56" s="9" t="n">
+        <v>13</v>
+      </c>
+      <c r="E56" s="8" t="inlineStr">
+        <is>
+          <t>RECAP</t>
+        </is>
+      </c>
       <c r="F56" s="8" t="inlineStr">
         <is>
-          <t>$INOD 100% gain achieved, make it free fam</t>
+          <t>$INFQ - $13 (S/L: 12)</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="8" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B57" s="8" t="inlineStr">
         <is>
-          <t>IREN</t>
+          <t>TE</t>
         </is>
       </c>
       <c r="C57" s="8" t="inlineStr">
@@ -3030,24 +3064,28 @@
         </is>
       </c>
       <c r="D57" s="9" t="n">
-        <v>60</v>
-      </c>
-      <c r="E57" s="8" t="inlineStr"/>
+        <v>7.4</v>
+      </c>
+      <c r="E57" s="8" t="inlineStr">
+        <is>
+          <t>RECAP</t>
+        </is>
+      </c>
       <c r="F57" s="8" t="inlineStr">
         <is>
-          <t>$IREN is just 3 handles shy of a double. Will be official at 60</t>
+          <t>$TE - $7.40</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="8" t="inlineStr">
         <is>
-          <t>2025-10-07</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B58" s="8" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C58" s="8" t="inlineStr">
@@ -3056,45 +3094,49 @@
         </is>
       </c>
       <c r="D58" s="9" t="n">
-        <v>8.83</v>
+        <v>10.33</v>
       </c>
       <c r="E58" s="8" t="inlineStr"/>
       <c r="F58" s="8" t="inlineStr">
         <is>
-          <t>$NB @ $8.83</t>
+          <t>$AMPX @ $10.33</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="8" t="inlineStr">
         <is>
-          <t>2025-10-08</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="B59" s="8" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>SATS</t>
         </is>
       </c>
       <c r="C59" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D59" s="9" t="n">
-        <v>6</v>
-      </c>
-      <c r="E59" s="8" t="inlineStr"/>
+        <v>89.59999999999999</v>
+      </c>
+      <c r="E59" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDE_INSERT</t>
+        </is>
+      </c>
       <c r="F59" s="8" t="inlineStr">
         <is>
-          <t>Buying $RXRX @ $6</t>
+          <t>Recap 9/17 confirms SATS 'sold after immediate large move' — full exit at same ~$89.60 level as the 9/8 harvest signal. Treats SATS as fully closed.</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="8" t="inlineStr">
         <is>
-          <t>2025-10-13</t>
+          <t>2025-10-02</t>
         </is>
       </c>
       <c r="B60" s="8" t="inlineStr">
@@ -3104,106 +3146,108 @@
       </c>
       <c r="C60" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
-        </is>
-      </c>
-      <c r="D60" s="9" t="n">
-        <v>83</v>
-      </c>
+          <t>TRIM</t>
+        </is>
+      </c>
+      <c r="D60" s="9" t="n"/>
       <c r="E60" s="8" t="inlineStr"/>
       <c r="F60" s="8" t="inlineStr">
         <is>
-          <t>i’m selling the remaining $INOD commons @ 83.</t>
+          <t>$INOD 100% gain achieved, make it free fam</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-06</t>
         </is>
       </c>
       <c r="B61" s="8" t="inlineStr">
         <is>
-          <t>RGTI</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C61" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D61" s="9" t="n">
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="E61" s="8" t="inlineStr"/>
       <c r="F61" s="8" t="inlineStr">
         <is>
-          <t>Closing out the remaining $RGTI position @ 45 to lock in the over 100% gain on commons.</t>
+          <t>$IREN is just 3 handles shy of a double. Will be official at 60</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="8" t="inlineStr">
         <is>
-          <t>2025-10-17</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B62" s="8" t="inlineStr">
         <is>
-          <t>SEI</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C62" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D62" s="9" t="n">
-        <v>50</v>
+        <v>8.83</v>
       </c>
       <c r="E62" s="8" t="inlineStr"/>
       <c r="F62" s="8" t="inlineStr">
         <is>
-          <t>Adding solar name $SEI @ 50 to the commons port</t>
+          <t>$NB @ $8.83</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="8" t="inlineStr">
         <is>
-          <t>2025-10-21</t>
+          <t>2025-10-07</t>
         </is>
       </c>
       <c r="B63" s="8" t="inlineStr">
         <is>
-          <t>KRKNF</t>
+          <t>IREN</t>
         </is>
       </c>
       <c r="C63" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D63" s="9" t="n">
-        <v>5</v>
-      </c>
-      <c r="E63" s="8" t="inlineStr"/>
+        <v>60</v>
+      </c>
+      <c r="E63" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDE_INSERT</t>
+        </is>
+      </c>
       <c r="F63" s="8" t="inlineStr">
         <is>
-          <t>$KRKNF @ $5</t>
+          <t>'Cost recouped' on 10/7 = 100% gain trim. Price ~$60 per 10/6 'will be official at 60' (the $30 entry × 2 = $60).</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-08</t>
         </is>
       </c>
       <c r="B64" s="8" t="inlineStr">
         <is>
-          <t>NB</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C64" s="8" t="inlineStr">
@@ -3212,193 +3256,189 @@
         </is>
       </c>
       <c r="D64" s="9" t="n">
-        <v>6.36</v>
+        <v>6</v>
       </c>
       <c r="E64" s="8" t="inlineStr"/>
       <c r="F64" s="8" t="inlineStr">
         <is>
-          <t>Selling $NB at 6.36 for a loss,</t>
+          <t>Buying $RXRX @ $6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-10-13</t>
         </is>
       </c>
       <c r="B65" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>INOD</t>
         </is>
       </c>
       <c r="C65" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D65" s="9" t="n">
-        <v>64.88</v>
+        <v>83</v>
       </c>
       <c r="E65" s="8" t="inlineStr"/>
       <c r="F65" s="8" t="inlineStr">
         <is>
-          <t>Replacing it with $MP at 64.88 but half sized.</t>
+          <t>i’m selling the remaining $INOD commons @ 83.</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B66" s="8" t="inlineStr">
         <is>
-          <t>MP</t>
+          <t>RGTI</t>
         </is>
       </c>
       <c r="C66" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D66" s="9" t="n">
-        <v>60.6</v>
-      </c>
-      <c r="E66" s="8" t="inlineStr">
-        <is>
-          <t>OVERRIDDEN</t>
-        </is>
-      </c>
+        <v>45</v>
+      </c>
+      <c r="E66" s="8" t="inlineStr"/>
       <c r="F66" s="8" t="inlineStr">
         <is>
-          <t>Dropping $RXRX from the commons port @ $4.18 and adding the other half of $MP @ 60.60</t>
+          <t>Closing out the remaining $RGTI position @ 45 to lock in the over 100% gain on commons.</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-10-17</t>
         </is>
       </c>
       <c r="B67" s="8" t="inlineStr">
         <is>
-          <t>RXRX</t>
+          <t>SEI</t>
         </is>
       </c>
       <c r="C67" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D67" s="9" t="n">
-        <v>4.18</v>
+        <v>50</v>
       </c>
       <c r="E67" s="8" t="inlineStr"/>
       <c r="F67" s="8" t="inlineStr">
         <is>
-          <t>Dropping $RXRX from the commons port @ $4.18 and adding the other half of $MP @ 60.60</t>
+          <t>Adding solar name $SEI @ 50 to the commons port</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-10-21</t>
         </is>
       </c>
       <c r="B68" s="8" t="inlineStr">
         <is>
-          <t>LDI</t>
+          <t>KRKNF</t>
         </is>
       </c>
       <c r="C68" s="8" t="inlineStr">
         <is>
-          <t>CLOSE</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D68" s="9" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="E68" s="8" t="inlineStr"/>
       <c r="F68" s="8" t="inlineStr">
         <is>
-          <t>Closing $LDI @ $2.3</t>
+          <t>$KRKNF @ $5</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="8" t="inlineStr">
         <is>
-          <t>2026-02-02</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B69" s="8" t="inlineStr">
         <is>
-          <t>SNDK</t>
+          <t>NB</t>
         </is>
       </c>
       <c r="C69" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D69" s="9" t="n">
-        <v>667</v>
+        <v>6.36</v>
       </c>
       <c r="E69" s="8" t="inlineStr"/>
       <c r="F69" s="8" t="inlineStr">
         <is>
-          <t>Adding $SNDK half sized @ 667</t>
+          <t>Selling $NB at 6.36 for a loss,</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="B70" s="8" t="inlineStr">
         <is>
-          <t>BBAI</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C70" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D70" s="9" t="n">
-        <v>4</v>
+        <v>64.88</v>
       </c>
       <c r="E70" s="8" t="inlineStr"/>
       <c r="F70" s="8" t="inlineStr">
         <is>
-          <t>$AXTI @ 44.75 to commons port and selling half of the $BBAI @ $4 that was previously 2x weighting.</t>
+          <t>Replacing it with $MP at 64.88 but half sized.</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="8" t="inlineStr">
         <is>
-          <t>2026-03-02</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B71" s="8" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>MP</t>
         </is>
       </c>
       <c r="C71" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D71" s="9" t="n">
-        <v>44.75</v>
+        <v>60.6</v>
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
@@ -3407,75 +3447,71 @@
       </c>
       <c r="F71" s="8" t="inlineStr">
         <is>
-          <t>$AXTI @ 44.75 to commons port and selling half of the $BBAI @ $4 that was previously 2x weighting.</t>
+          <t>Dropping $RXRX from the commons port @ $4.18 and adding the other half of $MP @ 60.60</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="8" t="inlineStr">
         <is>
-          <t>2026-03-10</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B72" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C72" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D72" s="9" t="n">
-        <v>15</v>
+        <v>4.18</v>
       </c>
       <c r="E72" s="8" t="inlineStr"/>
       <c r="F72" s="8" t="inlineStr">
         <is>
-          <t>$AMPX UP 77%, SELLING HALF HERE WITH STOP AT 15 ON REMAINDER</t>
+          <t>Dropping $RXRX from the commons port @ $4.18 and adding the other half of $MP @ 60.60</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="8" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B73" s="8" t="inlineStr">
         <is>
-          <t>INTC</t>
+          <t>LDI</t>
         </is>
       </c>
       <c r="C73" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>CLOSE</t>
         </is>
       </c>
       <c r="D73" s="9" t="n">
-        <v>83.88</v>
-      </c>
-      <c r="E73" s="8" t="inlineStr">
-        <is>
-          <t>OVERRIDE_INSERT</t>
-        </is>
-      </c>
+        <v>2.3</v>
+      </c>
+      <c r="E73" s="8" t="inlineStr"/>
       <c r="F73" s="8" t="inlineStr">
         <is>
-          <t>INTC up 150% — trim half. No price in source; computed $33.55 × 2.5. Position half-open after this.</t>
+          <t>Closing $LDI @ $2.3</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="8" t="inlineStr">
         <is>
-          <t>2026-04-27</t>
+          <t>2026-02-02</t>
         </is>
       </c>
       <c r="B74" s="8" t="inlineStr">
         <is>
-          <t>INFQ</t>
+          <t>SNDK</t>
         </is>
       </c>
       <c r="C74" s="8" t="inlineStr">
@@ -3484,28 +3520,24 @@
         </is>
       </c>
       <c r="D74" s="9" t="n">
-        <v>13</v>
-      </c>
-      <c r="E74" s="8" t="inlineStr">
-        <is>
-          <t>OVERRIDDEN</t>
-        </is>
-      </c>
+        <v>667</v>
+      </c>
+      <c r="E74" s="8" t="inlineStr"/>
       <c r="F74" s="8" t="inlineStr">
         <is>
-          <t>$INFQ @ $13 to commons port.</t>
+          <t>Adding $SNDK half sized @ 667</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="8" t="inlineStr">
         <is>
-          <t>2026-05-01</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B75" s="8" t="inlineStr">
         <is>
-          <t>AXTI</t>
+          <t>BBAI</t>
         </is>
       </c>
       <c r="C75" s="8" t="inlineStr">
@@ -3514,154 +3546,166 @@
         </is>
       </c>
       <c r="D75" s="9" t="n">
-        <v>98.59999999999999</v>
+        <v>4</v>
       </c>
       <c r="E75" s="8" t="inlineStr"/>
       <c r="F75" s="8" t="inlineStr">
         <is>
-          <t>$AXTI selling half of our position @ 98.60 for 120%</t>
+          <t>$AXTI @ 44.75 to commons port and selling half of the $BBAI @ $4 that was previously 2x weighting.</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-02</t>
         </is>
       </c>
       <c r="B76" s="8" t="inlineStr">
         <is>
-          <t>NVTS</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C76" s="8" t="inlineStr">
         <is>
-          <t>TRIM</t>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="D76" s="9" t="n">
-        <v>20.87</v>
-      </c>
-      <c r="E76" s="8" t="inlineStr"/>
+        <v>44.75</v>
+      </c>
+      <c r="E76" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDDEN</t>
+        </is>
+      </c>
       <c r="F76" s="8" t="inlineStr">
         <is>
-          <t>$NVTS 1/2 sold for @ 20.87 to lock in the 100% gain, standard practice.</t>
+          <t>$AXTI @ 44.75 to commons port and selling half of the $BBAI @ $4 that was previously 2x weighting.</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>2026-05-13</t>
+          <t>2026-03-10</t>
         </is>
       </c>
       <c r="B77" s="8" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>AMPX</t>
         </is>
       </c>
       <c r="C77" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D77" s="9" t="n"/>
+          <t>TRIM</t>
+        </is>
+      </c>
+      <c r="D77" s="9" t="n">
+        <v>15</v>
+      </c>
       <c r="E77" s="8" t="inlineStr"/>
       <c r="F77" s="8" t="inlineStr">
         <is>
-          <t>adding $LITE if we dip below 1K again, we should see this double again before the year is up</t>
+          <t>$AMPX UP 77%, SELLING HALF HERE WITH STOP AT 15 ON REMAINDER</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-24</t>
         </is>
       </c>
       <c r="B78" s="8" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>INTC</t>
         </is>
       </c>
       <c r="C78" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
-        </is>
-      </c>
-      <c r="D78" s="9" t="n"/>
-      <c r="E78" s="8" t="inlineStr"/>
+          <t>TRIM</t>
+        </is>
+      </c>
+      <c r="D78" s="9" t="n">
+        <v>83.88</v>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDE_INSERT</t>
+        </is>
+      </c>
       <c r="F78" s="8" t="inlineStr">
         <is>
-          <t>$LITE added to commons port.</t>
+          <t>INTC up 150% — trim half. No price in source; computed $33.55 × 2.5. Position half-open after this.</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="8" t="inlineStr">
         <is>
-          <t>2026-05-14</t>
+          <t>2026-04-27</t>
         </is>
       </c>
       <c r="B79" s="8" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>INFQ</t>
         </is>
       </c>
       <c r="C79" s="8" t="inlineStr">
         <is>
-          <t>OPEN</t>
+          <t>ADD</t>
         </is>
       </c>
       <c r="D79" s="9" t="n">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>OVERRIDE_INSERT</t>
+          <t>OVERRIDDEN</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
         <is>
-          <t>LITE 'added to commons' on 5/14 with no price. Context 'if we dip below 1K' suggests entry ~$1000.</t>
+          <t>$INFQ @ $13 to commons port.</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-01</t>
         </is>
       </c>
       <c r="B80" s="8" t="inlineStr">
         <is>
-          <t>TE</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C80" s="8" t="inlineStr">
         <is>
-          <t>ADD</t>
+          <t>TRIM</t>
         </is>
       </c>
       <c r="D80" s="9" t="n">
-        <v>7.4</v>
+        <v>98.59999999999999</v>
       </c>
       <c r="E80" s="8" t="inlineStr"/>
       <c r="F80" s="8" t="inlineStr">
         <is>
-          <t>Adding $TE @ 7.40</t>
+          <t>$AXTI selling half of our position @ 98.60 for 120%</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="8" t="inlineStr">
         <is>
-          <t>2026-05-18</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B81" s="8" t="inlineStr">
         <is>
-          <t>LITE</t>
+          <t>NVTS</t>
         </is>
       </c>
       <c r="C81" s="8" t="inlineStr">
@@ -3670,66 +3714,196 @@
         </is>
       </c>
       <c r="D81" s="9" t="n">
-        <v>886</v>
+        <v>20.87</v>
       </c>
       <c r="E81" s="8" t="inlineStr"/>
       <c r="F81" s="8" t="inlineStr">
         <is>
-          <t>reducing $LITE by 50% @ 886 ( plan to add back if 800 trades)</t>
+          <t>$NVTS 1/2 sold for @ 20.87 to lock in the 100% gain, standard practice.</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="8" t="inlineStr">
         <is>
-          <t>2026-05-21</t>
+          <t>2026-05-13</t>
         </is>
       </c>
       <c r="B82" s="8" t="inlineStr">
         <is>
-          <t>AMPX</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C82" s="8" t="inlineStr">
         <is>
-          <t>STOP</t>
-        </is>
-      </c>
-      <c r="D82" s="9" t="n">
-        <v>15</v>
-      </c>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D82" s="9" t="n"/>
       <c r="E82" s="8" t="inlineStr"/>
       <c r="F82" s="8" t="inlineStr">
         <is>
-          <t>$AMPX stopped @ $15 on remaining half of the original position from $10.33.</t>
+          <t>adding $LITE if we dip below 1K again, we should see this double again before the year is up</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="8" t="inlineStr">
         <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B83" s="8" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="C83" s="8" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D83" s="9" t="n"/>
+      <c r="E83" s="8" t="inlineStr"/>
+      <c r="F83" s="8" t="inlineStr">
+        <is>
+          <t>$LITE added to commons port.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-14</t>
+        </is>
+      </c>
+      <c r="B84" s="8" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="C84" s="8" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D84" s="9" t="n">
+        <v>1000</v>
+      </c>
+      <c r="E84" s="8" t="inlineStr">
+        <is>
+          <t>OVERRIDE_INSERT</t>
+        </is>
+      </c>
+      <c r="F84" s="8" t="inlineStr">
+        <is>
+          <t>LITE 'added to commons' on 5/14 with no price. Context 'if we dip below 1K' suggests entry ~$1000.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B85" s="8" t="inlineStr">
+        <is>
+          <t>TE</t>
+        </is>
+      </c>
+      <c r="C85" s="8" t="inlineStr">
+        <is>
+          <t>ADD</t>
+        </is>
+      </c>
+      <c r="D85" s="9" t="n">
+        <v>7.4</v>
+      </c>
+      <c r="E85" s="8" t="inlineStr"/>
+      <c r="F85" s="8" t="inlineStr">
+        <is>
+          <t>Adding $TE @ 7.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-18</t>
+        </is>
+      </c>
+      <c r="B86" s="8" t="inlineStr">
+        <is>
+          <t>LITE</t>
+        </is>
+      </c>
+      <c r="C86" s="8" t="inlineStr">
+        <is>
+          <t>TRIM</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="n">
+        <v>886</v>
+      </c>
+      <c r="E86" s="8" t="inlineStr"/>
+      <c r="F86" s="8" t="inlineStr">
+        <is>
+          <t>reducing $LITE by 50% @ 886 ( plan to add back if 800 trades)</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="8" t="inlineStr">
+        <is>
           <t>2026-05-21</t>
         </is>
       </c>
-      <c r="B83" s="8" t="inlineStr">
+      <c r="B87" s="8" t="inlineStr">
         <is>
           <t>AMPX</t>
         </is>
       </c>
-      <c r="C83" s="8" t="inlineStr">
+      <c r="C87" s="8" t="inlineStr">
+        <is>
+          <t>STOP</t>
+        </is>
+      </c>
+      <c r="D87" s="9" t="n">
+        <v>15</v>
+      </c>
+      <c r="E87" s="8" t="inlineStr"/>
+      <c r="F87" s="8" t="inlineStr">
+        <is>
+          <t>$AMPX stopped @ $15 on remaining half of the original position from $10.33.</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="8" t="inlineStr">
+        <is>
+          <t>2026-05-21</t>
+        </is>
+      </c>
+      <c r="B88" s="8" t="inlineStr">
+        <is>
+          <t>AMPX</t>
+        </is>
+      </c>
+      <c r="C88" s="8" t="inlineStr">
         <is>
           <t>ADD</t>
         </is>
       </c>
-      <c r="D83" s="9" t="n">
+      <c r="D88" s="9" t="n">
         <v>15.44</v>
       </c>
-      <c r="E83" s="8" t="inlineStr">
+      <c r="E88" s="8" t="inlineStr">
         <is>
           <t>OVERRIDE_INSERT</t>
         </is>
       </c>
-      <c r="F83" s="8" t="inlineStr">
+      <c r="F88" s="8" t="inlineStr">
         <is>
           <t>AMPX stopped at $15, then 'Adding back here @ $15.44 (half sized)'. Re-add missed by parser.</t>
         </is>
